--- a/data/nzd0469/nzd0469.xlsx
+++ b/data/nzd0469/nzd0469.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H371"/>
+  <dimension ref="A1:H374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11514,6 +11514,96 @@
       <c r="H371" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:26:55+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>293.37</v>
+      </c>
+      <c r="C372" t="n">
+        <v>283.85</v>
+      </c>
+      <c r="D372" t="n">
+        <v>269.58</v>
+      </c>
+      <c r="E372" t="n">
+        <v>267.99</v>
+      </c>
+      <c r="F372" t="n">
+        <v>280.04</v>
+      </c>
+      <c r="G372" t="n">
+        <v>283.85</v>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:33:05+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>293.41</v>
+      </c>
+      <c r="C373" t="n">
+        <v>282.19</v>
+      </c>
+      <c r="D373" t="n">
+        <v>270.4</v>
+      </c>
+      <c r="E373" t="n">
+        <v>268.22</v>
+      </c>
+      <c r="F373" t="n">
+        <v>276.11</v>
+      </c>
+      <c r="G373" t="n">
+        <v>350.47</v>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-28 22:33:10+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>293.25</v>
+      </c>
+      <c r="C374" t="n">
+        <v>283.93</v>
+      </c>
+      <c r="D374" t="n">
+        <v>271.3</v>
+      </c>
+      <c r="E374" t="n">
+        <v>268.33</v>
+      </c>
+      <c r="F374" t="n">
+        <v>274.16</v>
+      </c>
+      <c r="G374" t="n">
+        <v>391.05</v>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B504"/>
+  <dimension ref="A1:B507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16571,6 +16661,36 @@
       </c>
       <c r="B504" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2025-12-28 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>-0.52</v>
       </c>
     </row>
   </sheetData>
@@ -16739,28 +16859,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3435756070997679</v>
+        <v>0.3194730194193681</v>
       </c>
       <c r="J2" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K2" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1639021162522286</v>
+        <v>0.1396038402846148</v>
       </c>
       <c r="M2" t="n">
-        <v>4.653859601169938</v>
+        <v>4.738460788216743</v>
       </c>
       <c r="N2" t="n">
-        <v>34.52209808147774</v>
+        <v>36.34305756007951</v>
       </c>
       <c r="O2" t="n">
-        <v>5.875550874724662</v>
+        <v>6.02852034582944</v>
       </c>
       <c r="P2" t="n">
-        <v>300.633398805442</v>
+        <v>300.8809876093616</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16817,28 +16937,28 @@
         <v>0.07630000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3070912661946463</v>
+        <v>0.2951471986248708</v>
       </c>
       <c r="J3" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K3" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1447008026309233</v>
+        <v>0.1350996020130703</v>
       </c>
       <c r="M3" t="n">
-        <v>4.550971676404398</v>
+        <v>4.585890137282755</v>
       </c>
       <c r="N3" t="n">
-        <v>32.01121890349312</v>
+        <v>32.27473514667634</v>
       </c>
       <c r="O3" t="n">
-        <v>5.65784578293657</v>
+        <v>5.681085736606722</v>
       </c>
       <c r="P3" t="n">
-        <v>283.3370337958282</v>
+        <v>283.4596864580773</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16895,28 +17015,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4064485651283348</v>
+        <v>0.3867760658771549</v>
       </c>
       <c r="J4" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1830825279135396</v>
+        <v>0.166316363487783</v>
       </c>
       <c r="M4" t="n">
-        <v>4.878321280335853</v>
+        <v>4.943331332909943</v>
       </c>
       <c r="N4" t="n">
-        <v>42.28861859137058</v>
+        <v>43.35088716752659</v>
       </c>
       <c r="O4" t="n">
-        <v>6.502969982351955</v>
+        <v>6.584139060463911</v>
       </c>
       <c r="P4" t="n">
-        <v>273.0255338207948</v>
+        <v>273.227998377611</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16973,28 +17093,28 @@
         <v>0.0853</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3635147742935834</v>
+        <v>0.3470791141853695</v>
       </c>
       <c r="J5" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K5" t="n">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1539679065254819</v>
+        <v>0.1413741482002525</v>
       </c>
       <c r="M5" t="n">
-        <v>4.824767719015439</v>
+        <v>4.862259190818296</v>
       </c>
       <c r="N5" t="n">
-        <v>41.65640537303532</v>
+        <v>42.29640241933612</v>
       </c>
       <c r="O5" t="n">
-        <v>6.454177358349809</v>
+        <v>6.503568437353151</v>
       </c>
       <c r="P5" t="n">
-        <v>269.716257156905</v>
+        <v>269.8854180636845</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17051,28 +17171,28 @@
         <v>0.0968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2844037746783064</v>
+        <v>0.2846026399920483</v>
       </c>
       <c r="J6" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K6" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04666928045302399</v>
+        <v>0.04741509963526858</v>
       </c>
       <c r="M6" t="n">
-        <v>6.23602387644272</v>
+        <v>6.202278076524702</v>
       </c>
       <c r="N6" t="n">
-        <v>96.26298930084685</v>
+        <v>95.52533903476093</v>
       </c>
       <c r="O6" t="n">
-        <v>9.811370408910616</v>
+        <v>9.773706514662743</v>
       </c>
       <c r="P6" t="n">
-        <v>269.146725951776</v>
+        <v>269.1447441988482</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17129,28 +17249,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-7.26434792339432</v>
+        <v>-7.160301059903789</v>
       </c>
       <c r="J7" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="K7" t="n">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3324037072340209</v>
+        <v>0.3275024386749976</v>
       </c>
       <c r="M7" t="n">
-        <v>63.6914536832702</v>
+        <v>63.91476609581213</v>
       </c>
       <c r="N7" t="n">
-        <v>6048.856361634913</v>
+        <v>6053.912547309811</v>
       </c>
       <c r="O7" t="n">
-        <v>77.77439399722066</v>
+        <v>77.80689267224216</v>
       </c>
       <c r="P7" t="n">
-        <v>463.6018322444908</v>
+        <v>462.5207622083645</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17192,7 +17312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H371"/>
+  <dimension ref="A1:H374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32665,6 +32785,132 @@
         </is>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:26:55+00:00</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>-44.81572140877434,167.3917304580177</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>-44.815462245844365,167.39255365620664</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>-44.815240407873155,167.3934058632457</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>-44.81491892312604,167.39418063532185</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>-44.81449024851876,167.39487210796955</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>-44.81412632512931,167.3956139017008</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-12 22:33:05+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>-44.81572109443642,167.3917302137457</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>-44.8154752908237,167.3925637935954</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>-44.815233963990096,167.39340085556725</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>-44.81491711570107,167.39417923071844</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>-44.81452113182603,167.39489610847522</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>-44.813602802940274,167.39520705469104</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-28 22:33:10+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>-44.815722351788075,167.3917311908338</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>-44.81546161717065,167.3925531676579</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>-44.81522689143533,167.39339535933607</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-44.81491625128042,167.3941785589516</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>-44.814536455602976,167.39490801713222</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>-44.8132839112136,167.39495923690833</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0469/nzd0469.xlsx
+++ b/data/nzd0469/nzd0469.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H374"/>
+  <dimension ref="A1:H376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11604,6 +11604,66 @@
       <c r="H374" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>293.4</v>
+      </c>
+      <c r="C375" t="n">
+        <v>284.95</v>
+      </c>
+      <c r="D375" t="n">
+        <v>272.88</v>
+      </c>
+      <c r="E375" t="n">
+        <v>269.36</v>
+      </c>
+      <c r="F375" t="n">
+        <v>273.81</v>
+      </c>
+      <c r="G375" t="n">
+        <v>419.35</v>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-14 22:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>294.64</v>
+      </c>
+      <c r="C376" t="n">
+        <v>286.14</v>
+      </c>
+      <c r="D376" t="n">
+        <v>273.94</v>
+      </c>
+      <c r="E376" t="n">
+        <v>269.59</v>
+      </c>
+      <c r="F376" t="n">
+        <v>272.89</v>
+      </c>
+      <c r="G376" t="n">
+        <v>437.42</v>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B507"/>
+  <dimension ref="A1:B509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16691,6 +16751,26 @@
       </c>
       <c r="B507" t="n">
         <v>-0.52</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-01-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -16859,28 +16939,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3194730194193681</v>
+        <v>0.3045836577521221</v>
       </c>
       <c r="J2" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K2" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1396038402846148</v>
+        <v>0.125963007635385</v>
       </c>
       <c r="M2" t="n">
-        <v>4.738460788216743</v>
+        <v>4.790102989069402</v>
       </c>
       <c r="N2" t="n">
-        <v>36.34305756007951</v>
+        <v>37.38060107509725</v>
       </c>
       <c r="O2" t="n">
-        <v>6.02852034582944</v>
+        <v>6.113967703144763</v>
       </c>
       <c r="P2" t="n">
-        <v>300.8809876093616</v>
+        <v>301.0343886288915</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16937,28 +17017,28 @@
         <v>0.07630000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2951471986248708</v>
+        <v>0.2895976990918967</v>
       </c>
       <c r="J3" t="n">
+        <v>375</v>
+      </c>
+      <c r="K3" t="n">
         <v>373</v>
       </c>
-      <c r="K3" t="n">
-        <v>371</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1350996020130703</v>
+        <v>0.1312960274858096</v>
       </c>
       <c r="M3" t="n">
-        <v>4.585890137282755</v>
+        <v>4.595016157696528</v>
       </c>
       <c r="N3" t="n">
-        <v>32.27473514667634</v>
+        <v>32.27495600319284</v>
       </c>
       <c r="O3" t="n">
-        <v>5.681085736606722</v>
+        <v>5.681105174452664</v>
       </c>
       <c r="P3" t="n">
-        <v>283.4596864580773</v>
+        <v>283.5168415691011</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17015,28 +17095,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3867760658771549</v>
+        <v>0.3769933472572502</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L4" t="n">
-        <v>0.166316363487783</v>
+        <v>0.1590781297742662</v>
       </c>
       <c r="M4" t="n">
-        <v>4.943331332909943</v>
+        <v>4.970469258202379</v>
       </c>
       <c r="N4" t="n">
-        <v>43.35088716752659</v>
+        <v>43.6508349141998</v>
       </c>
       <c r="O4" t="n">
-        <v>6.584139060463911</v>
+        <v>6.60687784919623</v>
       </c>
       <c r="P4" t="n">
-        <v>273.227998377611</v>
+        <v>273.3289864527151</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17093,28 +17173,28 @@
         <v>0.0853</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3470791141853695</v>
+        <v>0.3377393961583657</v>
       </c>
       <c r="J5" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K5" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1413741482002525</v>
+        <v>0.1347557941690755</v>
       </c>
       <c r="M5" t="n">
-        <v>4.862259190818296</v>
+        <v>4.8805150715334</v>
       </c>
       <c r="N5" t="n">
-        <v>42.29640241933612</v>
+        <v>42.55344334949584</v>
       </c>
       <c r="O5" t="n">
-        <v>6.503568437353151</v>
+        <v>6.523300035219585</v>
       </c>
       <c r="P5" t="n">
-        <v>269.8854180636845</v>
+        <v>269.9818373571335</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17171,28 +17251,28 @@
         <v>0.0968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2846026399920483</v>
+        <v>0.2814010651607782</v>
       </c>
       <c r="J6" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K6" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04741509963526858</v>
+        <v>0.0468355499358224</v>
       </c>
       <c r="M6" t="n">
-        <v>6.202278076524702</v>
+        <v>6.189796036720918</v>
       </c>
       <c r="N6" t="n">
-        <v>95.52533903476093</v>
+        <v>95.06689694874295</v>
       </c>
       <c r="O6" t="n">
-        <v>9.773706514662743</v>
+        <v>9.750225481943634</v>
       </c>
       <c r="P6" t="n">
-        <v>269.1447441988482</v>
+        <v>269.1774933550577</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17249,28 +17329,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-7.160301059903789</v>
+        <v>-7.007283025512963</v>
       </c>
       <c r="J7" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K7" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3275024386749976</v>
+        <v>0.3156904024754732</v>
       </c>
       <c r="M7" t="n">
-        <v>63.91476609581213</v>
+        <v>64.68156897782598</v>
       </c>
       <c r="N7" t="n">
-        <v>6053.912547309811</v>
+        <v>6150.514851847016</v>
       </c>
       <c r="O7" t="n">
-        <v>77.80689267224216</v>
+        <v>78.42521821357602</v>
       </c>
       <c r="P7" t="n">
-        <v>462.5207622083645</v>
+        <v>460.927174688303</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17312,7 +17392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H374"/>
+  <dimension ref="A1:H376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32911,6 +32991,90 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-29 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>-44.8157211730209,167.39173027481368</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>-44.81545360158056,167.3925469386623</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>-44.81521447517202,167.3933857104</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-44.81490815715971,167.3941722687723</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>-44.81453920602439,167.39491015458412</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-44.81306151974492,167.3947864133448</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-14 22:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>-44.81571142854525,167.39172270238203</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>-44.81544425005847,167.39253967150287</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>-44.8152061452735,167.39337923706537</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-44.81490634973466,167.3941708641694</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>-44.81454643570336,167.39491577303005</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>-44.81291951915068,167.39467606341918</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0469/nzd0469.xlsx
+++ b/data/nzd0469/nzd0469.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H376"/>
+  <dimension ref="A1:H380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11664,6 +11664,126 @@
       <c r="H376" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-21 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>294.47</v>
+      </c>
+      <c r="C377" t="n">
+        <v>286.31</v>
+      </c>
+      <c r="D377" t="n">
+        <v>273.99</v>
+      </c>
+      <c r="E377" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="F377" t="n">
+        <v>271.62</v>
+      </c>
+      <c r="G377" t="n">
+        <v>449.88</v>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-29 22:32:59+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>296.22</v>
+      </c>
+      <c r="C378" t="n">
+        <v>288.38</v>
+      </c>
+      <c r="D378" t="n">
+        <v>275.03</v>
+      </c>
+      <c r="E378" t="n">
+        <v>269.76</v>
+      </c>
+      <c r="F378" t="n">
+        <v>271.56</v>
+      </c>
+      <c r="G378" t="n">
+        <v>457.79</v>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>299.77</v>
+      </c>
+      <c r="C379" t="n">
+        <v>291.98</v>
+      </c>
+      <c r="D379" t="n">
+        <v>277.97</v>
+      </c>
+      <c r="E379" t="n">
+        <v>271.34</v>
+      </c>
+      <c r="F379" t="n">
+        <v>271.56</v>
+      </c>
+      <c r="G379" t="n">
+        <v>445.97</v>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>299.77</v>
+      </c>
+      <c r="C380" t="n">
+        <v>291.98</v>
+      </c>
+      <c r="D380" t="n">
+        <v>276.76</v>
+      </c>
+      <c r="E380" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="F380" t="n">
+        <v>268.91</v>
+      </c>
+      <c r="G380" t="n">
+        <v>432.96</v>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11678,7 +11798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B509"/>
+  <dimension ref="A1:B513"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16771,6 +16891,46 @@
       </c>
       <c r="B509" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-01-21 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-01-29 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>-0.74</v>
       </c>
     </row>
   </sheetData>
@@ -16939,28 +17099,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3045836577521221</v>
+        <v>0.2826465904459999</v>
       </c>
       <c r="J2" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="L2" t="n">
-        <v>0.125963007635385</v>
+        <v>0.1087262155693308</v>
       </c>
       <c r="M2" t="n">
-        <v>4.790102989069402</v>
+        <v>4.856271532291166</v>
       </c>
       <c r="N2" t="n">
-        <v>37.38060107509725</v>
+        <v>38.40524884084139</v>
       </c>
       <c r="O2" t="n">
-        <v>6.113967703144763</v>
+        <v>6.197196853484758</v>
       </c>
       <c r="P2" t="n">
-        <v>301.0343886288915</v>
+        <v>301.2612542370853</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17017,28 +17177,28 @@
         <v>0.07630000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2895976990918967</v>
+        <v>0.286724870303013</v>
       </c>
       <c r="J3" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K3" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1312960274858096</v>
+        <v>0.1310502771067223</v>
       </c>
       <c r="M3" t="n">
-        <v>4.595016157696528</v>
+        <v>4.572719152351464</v>
       </c>
       <c r="N3" t="n">
-        <v>32.27495600319284</v>
+        <v>32.0182904762804</v>
       </c>
       <c r="O3" t="n">
-        <v>5.681105174452664</v>
+        <v>5.658470683522218</v>
       </c>
       <c r="P3" t="n">
-        <v>283.5168415691011</v>
+        <v>283.5464801989321</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17095,28 +17255,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3769933472572502</v>
+        <v>0.3629477382141197</v>
       </c>
       <c r="J4" t="n">
+        <v>379</v>
+      </c>
+      <c r="K4" t="n">
         <v>375</v>
       </c>
-      <c r="K4" t="n">
-        <v>371</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1590781297742662</v>
+        <v>0.150070484084873</v>
       </c>
       <c r="M4" t="n">
-        <v>4.970469258202379</v>
+        <v>4.99669548415913</v>
       </c>
       <c r="N4" t="n">
-        <v>43.6508349141998</v>
+        <v>43.77062400039301</v>
       </c>
       <c r="O4" t="n">
-        <v>6.60687784919623</v>
+        <v>6.61593712185908</v>
       </c>
       <c r="P4" t="n">
-        <v>273.3289864527151</v>
+        <v>273.474541798096</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17173,28 +17333,28 @@
         <v>0.0853</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3377393961583657</v>
+        <v>0.320589760456551</v>
       </c>
       <c r="J5" t="n">
+        <v>379</v>
+      </c>
+      <c r="K5" t="n">
         <v>375</v>
       </c>
-      <c r="K5" t="n">
-        <v>371</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.1347557941690755</v>
+        <v>0.1231283488523663</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8805150715334</v>
+        <v>4.91005956811011</v>
       </c>
       <c r="N5" t="n">
-        <v>42.55344334949584</v>
+        <v>42.94219002866888</v>
       </c>
       <c r="O5" t="n">
-        <v>6.523300035219585</v>
+        <v>6.553029072777633</v>
       </c>
       <c r="P5" t="n">
-        <v>269.9818373571335</v>
+        <v>270.1595999220468</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17251,28 +17411,28 @@
         <v>0.0968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2814010651607782</v>
+        <v>0.2705814592836407</v>
       </c>
       <c r="J6" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K6" t="n">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0468355499358224</v>
+        <v>0.04415218372335739</v>
       </c>
       <c r="M6" t="n">
-        <v>6.189796036720918</v>
+        <v>6.193711464513013</v>
       </c>
       <c r="N6" t="n">
-        <v>95.06689694874295</v>
+        <v>94.40060166804088</v>
       </c>
       <c r="O6" t="n">
-        <v>9.750225481943634</v>
+        <v>9.715997203995114</v>
       </c>
       <c r="P6" t="n">
-        <v>269.1774933550577</v>
+        <v>269.2886443930529</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17329,28 +17489,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-7.007283025512963</v>
+        <v>-6.676826418835771</v>
       </c>
       <c r="J7" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K7" t="n">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3156904024754732</v>
+        <v>0.289180538980223</v>
       </c>
       <c r="M7" t="n">
-        <v>64.68156897782598</v>
+        <v>66.38566609267257</v>
       </c>
       <c r="N7" t="n">
-        <v>6150.514851847016</v>
+        <v>6392.791295357455</v>
       </c>
       <c r="O7" t="n">
-        <v>78.42521821357602</v>
+        <v>79.9549329019633</v>
       </c>
       <c r="P7" t="n">
-        <v>460.927174688303</v>
+        <v>457.4720213735226</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17392,7 +17552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H376"/>
+  <dimension ref="A1:H380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33075,6 +33235,174 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-21 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>-44.815712764481454,167.39172374053786</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>-44.81544291412672,167.3925386333374</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>-44.81520575235375,167.39337893171944</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-44.814910121752156,167.39417379551472</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-44.81455641580334,167.3949235289304</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>-44.81282160391728,167.39459997296012</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-29 22:32:59+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>-44.81569901219668,167.391713053642</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>-44.815426647192396,167.39252599215</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>-44.81519757962285,167.39337258052504</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-44.81490501381179,167.3941698259847</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-44.814556887304114,167.39492389535098</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-44.8127594442264,167.39455166847128</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:26:48+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>-44.815671114702376,167.39169137452552</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>-44.81539835686927,167.3925040074926</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>-44.81517447593977,167.3933546261963</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-44.81489259758708,167.39416017697613</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-44.814556887304114,167.39492389535098</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>-44.81285233013035,167.39462385043709</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>-44.815671114702376,167.39169137452552</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>-44.81539835686927,167.3925040074926</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>-44.815183984598704,167.39336201556122</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-44.81490705698794,167.3941714137966</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-44.81457771192083,167.39494007893117</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>-44.812954567451065,167.39470329971107</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0469/nzd0469.xlsx
+++ b/data/nzd0469/nzd0469.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H380"/>
+  <dimension ref="A1:H381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11749,7 +11749,7 @@
         <v>271.56</v>
       </c>
       <c r="G379" t="n">
-        <v>445.97</v>
+        <v>457.79</v>
       </c>
       <c r="H379" t="inlineStr">
         <is>
@@ -11764,10 +11764,10 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>299.77</v>
+        <v>298.16</v>
       </c>
       <c r="C380" t="n">
-        <v>291.98</v>
+        <v>290.31</v>
       </c>
       <c r="D380" t="n">
         <v>276.76</v>
@@ -11779,9 +11779,39 @@
         <v>268.91</v>
       </c>
       <c r="G380" t="n">
-        <v>432.96</v>
+        <v>457.79</v>
       </c>
       <c r="H380" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>299.04</v>
+      </c>
+      <c r="C381" t="n">
+        <v>291.29</v>
+      </c>
+      <c r="D381" t="n">
+        <v>279.01</v>
+      </c>
+      <c r="E381" t="n">
+        <v>271.17</v>
+      </c>
+      <c r="F381" t="n">
+        <v>267.56</v>
+      </c>
+      <c r="G381" t="n">
+        <v>489.18</v>
+      </c>
+      <c r="H381" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11798,7 +11828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B513"/>
+  <dimension ref="A1:B514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16931,6 +16961,16 @@
       </c>
       <c r="B513" t="n">
         <v>-0.74</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
@@ -17099,28 +17139,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2826465904459999</v>
+        <v>0.2772629455042138</v>
       </c>
       <c r="J2" t="n">
+        <v>380</v>
+      </c>
+      <c r="K2" t="n">
         <v>379</v>
       </c>
-      <c r="K2" t="n">
-        <v>378</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.1087262155693308</v>
+        <v>0.10472451500874</v>
       </c>
       <c r="M2" t="n">
-        <v>4.856271532291166</v>
+        <v>4.872512838655313</v>
       </c>
       <c r="N2" t="n">
-        <v>38.40524884084139</v>
+        <v>38.63379986326402</v>
       </c>
       <c r="O2" t="n">
-        <v>6.197196853484758</v>
+        <v>6.215609371836685</v>
       </c>
       <c r="P2" t="n">
-        <v>301.2612542370853</v>
+        <v>301.3171360065394</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17177,28 +17217,28 @@
         <v>0.07630000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.286724870303013</v>
+        <v>0.2860012273704836</v>
       </c>
       <c r="J3" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K3" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1310502771067223</v>
+        <v>0.1310497895261514</v>
       </c>
       <c r="M3" t="n">
-        <v>4.572719152351464</v>
+        <v>4.56152168804764</v>
       </c>
       <c r="N3" t="n">
-        <v>32.0182904762804</v>
+        <v>31.93362581499185</v>
       </c>
       <c r="O3" t="n">
-        <v>5.658470683522218</v>
+        <v>5.650984499624101</v>
       </c>
       <c r="P3" t="n">
-        <v>283.5464801989321</v>
+        <v>283.5539827473792</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17255,28 +17295,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3629477382141197</v>
+        <v>0.3609960609974282</v>
       </c>
       <c r="J4" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K4" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L4" t="n">
-        <v>0.150070484084873</v>
+        <v>0.1492117965000798</v>
       </c>
       <c r="M4" t="n">
-        <v>4.99669548415913</v>
+        <v>4.994513629098922</v>
       </c>
       <c r="N4" t="n">
-        <v>43.77062400039301</v>
+        <v>43.69846921974693</v>
       </c>
       <c r="O4" t="n">
-        <v>6.61593712185908</v>
+        <v>6.610481769110851</v>
       </c>
       <c r="P4" t="n">
-        <v>273.474541798096</v>
+        <v>273.4948443909955</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17333,28 +17373,28 @@
         <v>0.0853</v>
       </c>
       <c r="I5" t="n">
-        <v>0.320589760456551</v>
+        <v>0.3170207630281994</v>
       </c>
       <c r="J5" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K5" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1231283488523663</v>
+        <v>0.1209011281794918</v>
       </c>
       <c r="M5" t="n">
-        <v>4.91005956811011</v>
+        <v>4.914406209383136</v>
       </c>
       <c r="N5" t="n">
-        <v>42.94219002866888</v>
+        <v>42.97597913816556</v>
       </c>
       <c r="O5" t="n">
-        <v>6.553029072777633</v>
+        <v>6.555606694896023</v>
       </c>
       <c r="P5" t="n">
-        <v>270.1595999220468</v>
+        <v>270.1967269127334</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17411,28 +17451,28 @@
         <v>0.0968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2705814592836407</v>
+        <v>0.2663668698843401</v>
       </c>
       <c r="J6" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K6" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04415218372335739</v>
+        <v>0.04296044125580134</v>
       </c>
       <c r="M6" t="n">
-        <v>6.193711464513013</v>
+        <v>6.204509604953675</v>
       </c>
       <c r="N6" t="n">
-        <v>94.40060166804088</v>
+        <v>94.35878043668761</v>
       </c>
       <c r="O6" t="n">
-        <v>9.715997203995114</v>
+        <v>9.713844781377125</v>
       </c>
       <c r="P6" t="n">
-        <v>269.2886443930529</v>
+        <v>269.3320849885008</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17489,28 +17529,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.676826418835771</v>
+        <v>-6.558467182253995</v>
       </c>
       <c r="J7" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K7" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L7" t="n">
-        <v>0.289180538980223</v>
+        <v>0.2782119718169707</v>
       </c>
       <c r="M7" t="n">
-        <v>66.38566609267257</v>
+        <v>67.07573471918747</v>
       </c>
       <c r="N7" t="n">
-        <v>6392.791295357455</v>
+        <v>6525.486637010401</v>
       </c>
       <c r="O7" t="n">
-        <v>79.9549329019633</v>
+        <v>80.78048425833062</v>
       </c>
       <c r="P7" t="n">
-        <v>457.4720213735226</v>
+        <v>456.2302640586729</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17552,7 +17592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H380"/>
+  <dimension ref="A1:H381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33352,7 +33392,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>-44.81285233013035,167.39462385043709</t>
+          <t>-44.8127594442264,167.39455166847128</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -33369,12 +33409,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>-44.815671114702376,167.39169137452552</t>
+          <t>-44.81568376680582,167.39170120646037</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>-44.81539835686927,167.3925040074926</t>
+          <t>-44.81541148043623,167.39251420592834</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -33394,10 +33434,52 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>-44.812954567451065,167.39470329971107</t>
+          <t>-44.8127594442264,167.39455166847128</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:32:52+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>-44.81567685137047,167.39169583248304</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>-44.815403779181445,167.392508221217</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-44.81516630320781,167.39334827500846</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-44.81489393351002,167.3941612151604</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-44.814588320687164,167.39494832340088</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>-44.81251276989998,167.3943599781895</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0469/nzd0469.xlsx
+++ b/data/nzd0469/nzd0469.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H381"/>
+  <dimension ref="A1:H383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11806,12 +11806,72 @@
         <v>271.17</v>
       </c>
       <c r="F381" t="n">
-        <v>267.56</v>
+        <v>269.02</v>
       </c>
       <c r="G381" t="n">
         <v>489.18</v>
       </c>
       <c r="H381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:21+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>300.49</v>
+      </c>
+      <c r="C382" t="n">
+        <v>292.27</v>
+      </c>
+      <c r="D382" t="n">
+        <v>279.82</v>
+      </c>
+      <c r="E382" t="n">
+        <v>272.22</v>
+      </c>
+      <c r="F382" t="n">
+        <v>270.47</v>
+      </c>
+      <c r="G382" t="n">
+        <v>494.16</v>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-19 22:32:31+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>300.74</v>
+      </c>
+      <c r="C383" t="n">
+        <v>292.4</v>
+      </c>
+      <c r="D383" t="n">
+        <v>280.88</v>
+      </c>
+      <c r="E383" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="F383" t="n">
+        <v>271.37</v>
+      </c>
+      <c r="G383" t="n">
+        <v>494.16</v>
+      </c>
+      <c r="H383" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11828,7 +11888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B514"/>
+  <dimension ref="A1:B516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16971,6 +17031,26 @@
       </c>
       <c r="B514" t="n">
         <v>0.96</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-04-19 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -17139,28 +17219,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2772629455042138</v>
+        <v>0.2696370357192066</v>
       </c>
       <c r="J2" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K2" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L2" t="n">
-        <v>0.10472451500874</v>
+        <v>0.09973301281553593</v>
       </c>
       <c r="M2" t="n">
-        <v>4.872512838655313</v>
+        <v>4.887995497437913</v>
       </c>
       <c r="N2" t="n">
-        <v>38.63379986326402</v>
+        <v>38.76857749462427</v>
       </c>
       <c r="O2" t="n">
-        <v>6.215609371836685</v>
+        <v>6.226441800468729</v>
       </c>
       <c r="P2" t="n">
-        <v>301.3171360065394</v>
+        <v>301.3966535830919</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17217,28 +17297,28 @@
         <v>0.07630000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2860012273704836</v>
+        <v>0.2871069791319765</v>
       </c>
       <c r="J3" t="n">
+        <v>382</v>
+      </c>
+      <c r="K3" t="n">
         <v>380</v>
       </c>
-      <c r="K3" t="n">
-        <v>378</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1310497895261514</v>
+        <v>0.1330679653913629</v>
       </c>
       <c r="M3" t="n">
-        <v>4.56152168804764</v>
+        <v>4.542836408664719</v>
       </c>
       <c r="N3" t="n">
-        <v>31.93362581499185</v>
+        <v>31.77268261578731</v>
       </c>
       <c r="O3" t="n">
-        <v>5.650984499624101</v>
+        <v>5.636726232112689</v>
       </c>
       <c r="P3" t="n">
-        <v>283.5539827473792</v>
+        <v>283.5424538614352</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17295,28 +17375,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3609960609974282</v>
+        <v>0.3583931971089608</v>
       </c>
       <c r="J4" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K4" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1492117965000798</v>
+        <v>0.1485399998395709</v>
       </c>
       <c r="M4" t="n">
-        <v>4.994513629098922</v>
+        <v>4.982704175562003</v>
       </c>
       <c r="N4" t="n">
-        <v>43.69846921974693</v>
+        <v>43.50811965409229</v>
       </c>
       <c r="O4" t="n">
-        <v>6.610481769110851</v>
+        <v>6.596068499802916</v>
       </c>
       <c r="P4" t="n">
-        <v>273.4948443909955</v>
+        <v>273.5220317196171</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17373,28 +17453,28 @@
         <v>0.0853</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3170207630281994</v>
+        <v>0.3116206706772411</v>
       </c>
       <c r="J5" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K5" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1209011281794918</v>
+        <v>0.1179282308550993</v>
       </c>
       <c r="M5" t="n">
-        <v>4.914406209383136</v>
+        <v>4.915234337337316</v>
       </c>
       <c r="N5" t="n">
-        <v>42.97597913816556</v>
+        <v>42.92088053637917</v>
       </c>
       <c r="O5" t="n">
-        <v>6.555606694896023</v>
+        <v>6.551402944131827</v>
       </c>
       <c r="P5" t="n">
-        <v>270.1967269127334</v>
+        <v>270.2531396977508</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17451,28 +17531,28 @@
         <v>0.0968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2663668698843401</v>
+        <v>0.2618824901903955</v>
       </c>
       <c r="J6" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K6" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04296044125580134</v>
+        <v>0.04194695726132247</v>
       </c>
       <c r="M6" t="n">
-        <v>6.204509604953675</v>
+        <v>6.200326002240531</v>
       </c>
       <c r="N6" t="n">
-        <v>94.35878043668761</v>
+        <v>93.95387813713948</v>
       </c>
       <c r="O6" t="n">
-        <v>9.713844781377125</v>
+        <v>9.692980869533349</v>
       </c>
       <c r="P6" t="n">
-        <v>269.3320849885008</v>
+        <v>269.3785413264692</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17529,28 +17609,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.558467182253995</v>
+        <v>-6.354893971914149</v>
       </c>
       <c r="J7" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K7" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2782119718169707</v>
+        <v>0.2606586784721489</v>
       </c>
       <c r="M7" t="n">
-        <v>67.07573471918747</v>
+        <v>68.29531593298019</v>
       </c>
       <c r="N7" t="n">
-        <v>6525.486637010401</v>
+        <v>6729.884950286038</v>
       </c>
       <c r="O7" t="n">
-        <v>80.78048425833062</v>
+        <v>82.03587599511593</v>
       </c>
       <c r="P7" t="n">
-        <v>456.2302640586729</v>
+        <v>454.0842475317572</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17592,7 +17672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H381"/>
+  <dimension ref="A1:H383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33471,7 +33551,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>-44.814588320687164,167.39494832340088</t>
+          <t>-44.81457684750283,167.3949394071597</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
@@ -33480,6 +33560,90 @@
         </is>
       </c>
       <c r="H381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:21+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>-44.815665456618646,167.39168697763674</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>-44.81539607792643,167.3925022365072</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-44.81515993790679,167.39334332841148</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-44.81488568222115,167.3941548028465</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-44.8145654529014,167.39493055199202</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>-44.81247363518002,167.39432956681415</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-19 22:32:31+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>-44.8156634920062,167.3916854509394</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>-44.81539505633137,167.39250144261726</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-44.81515160800642,167.39333685508856</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-44.814874601918525,167.39414619202773</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>-44.81455838038991,167.39492505568276</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>-44.81247363518002,167.39432956681415</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0469/nzd0469.xlsx
+++ b/data/nzd0469/nzd0469.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H383"/>
+  <dimension ref="A1:H384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11874,6 +11874,36 @@
       <c r="H383" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:26:06+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>300.87</v>
+      </c>
+      <c r="C384" t="n">
+        <v>292.38</v>
+      </c>
+      <c r="D384" t="n">
+        <v>282.54</v>
+      </c>
+      <c r="E384" t="n">
+        <v>275.36</v>
+      </c>
+      <c r="F384" t="n">
+        <v>271.49</v>
+      </c>
+      <c r="G384" t="n">
+        <v>494.16</v>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B516"/>
+  <dimension ref="A1:B519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17051,6 +17081,36 @@
       </c>
       <c r="B516" t="n">
         <v>0.21</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-05-22 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>-0.75</v>
       </c>
     </row>
   </sheetData>
@@ -17219,28 +17279,28 @@
         <v>0.06759999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2696370357192066</v>
+        <v>0.26601013348999</v>
       </c>
       <c r="J2" t="n">
+        <v>383</v>
+      </c>
+      <c r="K2" t="n">
         <v>382</v>
       </c>
-      <c r="K2" t="n">
-        <v>381</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.09973301281553593</v>
+        <v>0.09741892028887844</v>
       </c>
       <c r="M2" t="n">
-        <v>4.887995497437913</v>
+        <v>4.894740528245575</v>
       </c>
       <c r="N2" t="n">
-        <v>38.76857749462427</v>
+        <v>38.82159124275507</v>
       </c>
       <c r="O2" t="n">
-        <v>6.226441800468729</v>
+        <v>6.23069749247667</v>
       </c>
       <c r="P2" t="n">
-        <v>301.3966535830919</v>
+        <v>301.4345589431946</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17297,28 +17357,28 @@
         <v>0.07630000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2871069791319765</v>
+        <v>0.2876623008766784</v>
       </c>
       <c r="J3" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K3" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1330679653913629</v>
+        <v>0.134083194483898</v>
       </c>
       <c r="M3" t="n">
-        <v>4.542836408664719</v>
+        <v>4.53357816587807</v>
       </c>
       <c r="N3" t="n">
-        <v>31.77268261578731</v>
+        <v>31.69292222558643</v>
       </c>
       <c r="O3" t="n">
-        <v>5.636726232112689</v>
+        <v>5.629646722982396</v>
       </c>
       <c r="P3" t="n">
-        <v>283.5424538614352</v>
+        <v>283.5366513549337</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17375,28 +17435,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3583931971089608</v>
+        <v>0.3581393875896778</v>
       </c>
       <c r="J4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K4" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1485399998395709</v>
+        <v>0.1489940690745777</v>
       </c>
       <c r="M4" t="n">
-        <v>4.982704175562003</v>
+        <v>4.970971149824047</v>
       </c>
       <c r="N4" t="n">
-        <v>43.50811965409229</v>
+        <v>43.39408070645337</v>
       </c>
       <c r="O4" t="n">
-        <v>6.596068499802916</v>
+        <v>6.587418364310359</v>
       </c>
       <c r="P4" t="n">
-        <v>273.5220317196171</v>
+        <v>273.5246899035706</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17453,28 +17513,28 @@
         <v>0.0853</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3116206706772411</v>
+        <v>0.3101105205671432</v>
       </c>
       <c r="J5" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K5" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1179282308550993</v>
+        <v>0.1173756892624779</v>
       </c>
       <c r="M5" t="n">
-        <v>4.915234337337316</v>
+        <v>4.909854256738082</v>
       </c>
       <c r="N5" t="n">
-        <v>42.92088053637917</v>
+        <v>42.83447448366226</v>
       </c>
       <c r="O5" t="n">
-        <v>6.551402944131827</v>
+        <v>6.544805152459641</v>
       </c>
       <c r="P5" t="n">
-        <v>270.2531396977508</v>
+        <v>270.2689557191572</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17531,28 +17591,28 @@
         <v>0.0968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2618824901903955</v>
+        <v>0.2596031422207318</v>
       </c>
       <c r="J6" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K6" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04194695726132247</v>
+        <v>0.04142145301336142</v>
       </c>
       <c r="M6" t="n">
-        <v>6.200326002240531</v>
+        <v>6.198458040626596</v>
       </c>
       <c r="N6" t="n">
-        <v>93.95387813713948</v>
+        <v>93.76705508368313</v>
       </c>
       <c r="O6" t="n">
-        <v>9.692980869533349</v>
+        <v>9.683339046201116</v>
       </c>
       <c r="P6" t="n">
-        <v>269.3785413264692</v>
+        <v>269.4021974169186</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17609,28 +17669,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.354893971914149</v>
+        <v>-6.254877775730505</v>
       </c>
       <c r="J7" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K7" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2606586784721489</v>
+        <v>0.2522698257861149</v>
       </c>
       <c r="M7" t="n">
-        <v>68.29531593298019</v>
+        <v>68.90356851340135</v>
       </c>
       <c r="N7" t="n">
-        <v>6729.884950286038</v>
+        <v>6828.837218825723</v>
       </c>
       <c r="O7" t="n">
-        <v>82.03587599511593</v>
+        <v>82.63677885073766</v>
       </c>
       <c r="P7" t="n">
-        <v>454.0842475317572</v>
+        <v>453.0274817971291</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17672,7 +17732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H383"/>
+  <dimension ref="A1:H384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33649,6 +33709,48 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:26:06+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>-44.815662470407716,167.39168465705686</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>-44.81539521349984,167.39250156475416</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-44.815138563067535,167.3933267176242</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-44.81486100693662,167.39413562698488</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-44.81455743738836,167.3949243228416</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>-44.81247363518002,167.39432956681415</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0469/nzd0469.xlsx
+++ b/data/nzd0469/nzd0469.xlsx
@@ -11918,7 +11918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B519"/>
+  <dimension ref="A1:B520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17111,6 +17111,16 @@
       </c>
       <c r="B519" t="n">
         <v>-0.75</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-06-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>-0.62</v>
       </c>
     </row>
   </sheetData>
